--- a/upload/working_hour.xlsx
+++ b/upload/working_hour.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="158">
   <si>
     <t>Code</t>
   </si>
@@ -482,19 +482,13 @@
     <t>Upload Time</t>
   </si>
   <si>
-    <t>Success</t>
-  </si>
-  <si>
-    <t>2024-02-18 19:36:50</t>
-  </si>
-  <si>
-    <t>Error - No change</t>
+    <t>Success - No change</t>
+  </si>
+  <si>
+    <t>2024-02-18 21:03:25</t>
   </si>
   <si>
     <t>Error - No Employee</t>
-  </si>
-  <si>
-    <t>2024-02-18 19:36:51</t>
   </si>
 </sst>
 </file>
@@ -894,7 +888,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>156</v>
@@ -911,7 +905,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>156</v>
@@ -928,7 +922,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>156</v>
@@ -945,7 +939,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>156</v>
@@ -962,7 +956,7 @@
         <v>7</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>156</v>
@@ -979,7 +973,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>156</v>
@@ -996,7 +990,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>156</v>
@@ -1013,7 +1007,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>156</v>
@@ -1030,7 +1024,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>156</v>
@@ -1047,7 +1041,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>156</v>
@@ -1064,7 +1058,7 @@
         <v>7</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>156</v>
@@ -1081,7 +1075,7 @@
         <v>18</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>156</v>
@@ -1098,7 +1092,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>156</v>
@@ -1115,7 +1109,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>156</v>
@@ -1132,7 +1126,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>156</v>
@@ -1149,7 +1143,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>156</v>
@@ -1166,7 +1160,7 @@
         <v>29</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>156</v>
@@ -1183,7 +1177,7 @@
         <v>7</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>156</v>
@@ -1200,7 +1194,7 @@
         <v>13</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>156</v>
@@ -1217,7 +1211,7 @@
         <v>11</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>156</v>
@@ -1234,7 +1228,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>156</v>
@@ -1251,7 +1245,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>156</v>
@@ -1268,7 +1262,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>156</v>
@@ -1285,7 +1279,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>156</v>
@@ -1302,7 +1296,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>156</v>
@@ -1319,7 +1313,7 @@
         <v>13</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>156</v>
@@ -1336,7 +1330,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>156</v>
@@ -1353,7 +1347,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>156</v>
@@ -1370,7 +1364,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>156</v>
@@ -1387,7 +1381,7 @@
         <v>7</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>156</v>
@@ -1404,7 +1398,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>156</v>
@@ -1421,7 +1415,7 @@
         <v>7</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>156</v>
@@ -1438,7 +1432,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>156</v>
@@ -1455,7 +1449,7 @@
         <v>11</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>156</v>
@@ -1472,7 +1466,7 @@
         <v>11</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>156</v>
@@ -1489,7 +1483,7 @@
         <v>7</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>156</v>
@@ -1506,7 +1500,7 @@
         <v>7</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>156</v>
@@ -1523,7 +1517,7 @@
         <v>13</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>156</v>
@@ -1540,7 +1534,7 @@
         <v>11</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>156</v>
@@ -1557,7 +1551,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>156</v>
@@ -1574,7 +1568,7 @@
         <v>13</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>156</v>
@@ -1591,7 +1585,7 @@
         <v>9</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>156</v>
@@ -1608,7 +1602,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>156</v>
@@ -1625,7 +1619,7 @@
         <v>7</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>156</v>
@@ -1642,7 +1636,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>156</v>
@@ -1659,7 +1653,7 @@
         <v>11</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>156</v>
@@ -1676,7 +1670,7 @@
         <v>13</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>156</v>
@@ -1693,7 +1687,7 @@
         <v>7</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>156</v>
@@ -1710,7 +1704,7 @@
         <v>13</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>156</v>
@@ -1727,7 +1721,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>156</v>
@@ -1744,7 +1738,7 @@
         <v>29</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>156</v>
@@ -1761,7 +1755,7 @@
         <v>7</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>156</v>
@@ -1778,7 +1772,7 @@
         <v>5</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>156</v>
@@ -1795,7 +1789,7 @@
         <v>13</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>156</v>
@@ -1812,7 +1806,7 @@
         <v>13</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>156</v>
@@ -1829,7 +1823,7 @@
         <v>29</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>156</v>
@@ -1846,7 +1840,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>156</v>
@@ -1863,7 +1857,7 @@
         <v>7</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>156</v>
@@ -1880,7 +1874,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>156</v>
@@ -1897,7 +1891,7 @@
         <v>9</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>156</v>
@@ -1914,7 +1908,7 @@
         <v>29</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>156</v>
@@ -1931,7 +1925,7 @@
         <v>9</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>156</v>
@@ -1948,7 +1942,7 @@
         <v>7</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>156</v>
@@ -1965,7 +1959,7 @@
         <v>7</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>156</v>
@@ -1982,7 +1976,7 @@
         <v>9</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>156</v>
@@ -1999,7 +1993,7 @@
         <v>9</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>156</v>
@@ -2016,7 +2010,7 @@
         <v>7</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>156</v>
@@ -2033,7 +2027,7 @@
         <v>9</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>156</v>
@@ -2050,7 +2044,7 @@
         <v>11</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>156</v>
@@ -2067,7 +2061,7 @@
         <v>7</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>156</v>
@@ -2084,7 +2078,7 @@
         <v>9</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>156</v>
@@ -2101,7 +2095,7 @@
         <v>9</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>156</v>
@@ -2118,7 +2112,7 @@
         <v>9</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>156</v>
@@ -2135,7 +2129,7 @@
         <v>11</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>156</v>
@@ -2152,7 +2146,7 @@
         <v>29</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>156</v>
@@ -2169,7 +2163,7 @@
         <v>11</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>156</v>
@@ -2186,7 +2180,7 @@
         <v>29</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>156</v>
@@ -2203,7 +2197,7 @@
         <v>9</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>156</v>
@@ -2220,7 +2214,7 @@
         <v>9</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>156</v>
@@ -2237,7 +2231,7 @@
         <v>7</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>156</v>
@@ -2254,7 +2248,7 @@
         <v>13</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>156</v>
@@ -2271,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>156</v>
@@ -2288,7 +2282,7 @@
         <v>7</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>156</v>
@@ -2305,7 +2299,7 @@
         <v>5</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>156</v>
@@ -2322,7 +2316,7 @@
         <v>9</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>156</v>
@@ -2339,7 +2333,7 @@
         <v>9</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>156</v>
@@ -2356,7 +2350,7 @@
         <v>13</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>156</v>
@@ -2373,7 +2367,7 @@
         <v>7</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>156</v>
@@ -2390,7 +2384,7 @@
         <v>11</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>156</v>
@@ -2407,7 +2401,7 @@
         <v>7</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>156</v>
@@ -2424,7 +2418,7 @@
         <v>105</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>156</v>
@@ -2441,7 +2435,7 @@
         <v>13</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>156</v>
@@ -2458,7 +2452,7 @@
         <v>9</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>156</v>
@@ -2475,7 +2469,7 @@
         <v>7</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>156</v>
@@ -2492,7 +2486,7 @@
         <v>9</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>156</v>
@@ -2509,7 +2503,7 @@
         <v>7</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>156</v>
@@ -2526,7 +2520,7 @@
         <v>9</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>156</v>
@@ -2543,7 +2537,7 @@
         <v>9</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>156</v>
@@ -2560,7 +2554,7 @@
         <v>13</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>156</v>
@@ -2577,7 +2571,7 @@
         <v>13</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>156</v>
@@ -2594,7 +2588,7 @@
         <v>7</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>156</v>
@@ -2611,7 +2605,7 @@
         <v>7</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>156</v>
@@ -2628,7 +2622,7 @@
         <v>9</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>156</v>
@@ -2645,7 +2639,7 @@
         <v>7</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>156</v>
@@ -2662,7 +2656,7 @@
         <v>29</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>156</v>
@@ -2679,7 +2673,7 @@
         <v>9</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>156</v>
@@ -2696,7 +2690,7 @@
         <v>13</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>156</v>
@@ -2713,7 +2707,7 @@
         <v>13</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>156</v>
@@ -2730,7 +2724,7 @@
         <v>13</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>156</v>
@@ -2747,7 +2741,7 @@
         <v>13</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>156</v>
@@ -2764,7 +2758,7 @@
         <v>11</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>156</v>
@@ -2781,7 +2775,7 @@
         <v>9</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>156</v>
@@ -2798,7 +2792,7 @@
         <v>9</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>156</v>
@@ -2815,7 +2809,7 @@
         <v>11</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>156</v>
@@ -2832,7 +2826,7 @@
         <v>7</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>156</v>
@@ -2849,7 +2843,7 @@
         <v>7</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>156</v>
@@ -2866,7 +2860,7 @@
         <v>7</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>156</v>
@@ -2883,7 +2877,7 @@
         <v>9</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>156</v>
@@ -2900,7 +2894,7 @@
         <v>7</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>156</v>
@@ -2917,7 +2911,7 @@
         <v>13</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>156</v>
@@ -2934,7 +2928,7 @@
         <v>7</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>156</v>
@@ -2951,7 +2945,7 @@
         <v>7</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>156</v>
@@ -2968,7 +2962,7 @@
         <v>9</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>156</v>
@@ -2985,7 +2979,7 @@
         <v>7</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>156</v>
@@ -3002,7 +2996,7 @@
         <v>11</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>156</v>
@@ -3019,7 +3013,7 @@
         <v>11</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>156</v>
@@ -3036,7 +3030,7 @@
         <v>9</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>156</v>
@@ -3053,7 +3047,7 @@
         <v>9</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>156</v>
@@ -3070,7 +3064,7 @@
         <v>7</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>156</v>
@@ -3087,7 +3081,7 @@
         <v>7</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>156</v>
@@ -3104,7 +3098,7 @@
         <v>7</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>156</v>
@@ -3121,7 +3115,7 @@
         <v>13</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>156</v>
@@ -3138,7 +3132,7 @@
         <v>13</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>156</v>
@@ -3155,7 +3149,7 @@
         <v>7</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>156</v>
@@ -3172,7 +3166,7 @@
         <v>7</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>156</v>
@@ -3189,7 +3183,7 @@
         <v>7</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>156</v>
@@ -3206,7 +3200,7 @@
         <v>13</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>156</v>
@@ -3223,10 +3217,10 @@
         <v>7</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/upload/working_hour.xlsx
+++ b/upload/working_hour.xlsx
@@ -482,10 +482,10 @@
     <t>Upload Time</t>
   </si>
   <si>
-    <t>Success - No change</t>
-  </si>
-  <si>
-    <t>2024-02-18 21:03:25</t>
+    <t>2024-02-24 18:36:29</t>
+  </si>
+  <si>
+    <t>Success</t>
   </si>
   <si>
     <t>Error - No Employee</t>
@@ -871,10 +871,10 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -888,10 +888,10 @@
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -905,10 +905,10 @@
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -922,10 +922,10 @@
         <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -939,10 +939,10 @@
         <v>13</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -956,10 +956,10 @@
         <v>7</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -973,10 +973,10 @@
         <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -990,10 +990,10 @@
         <v>18</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1007,10 +1007,10 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1024,10 +1024,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1041,10 +1041,10 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1058,10 +1058,10 @@
         <v>7</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1075,10 +1075,10 @@
         <v>18</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1092,10 +1092,10 @@
         <v>9</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1109,10 +1109,10 @@
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1126,10 +1126,10 @@
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1143,10 +1143,10 @@
         <v>9</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1160,10 +1160,10 @@
         <v>29</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1177,10 +1177,10 @@
         <v>7</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1194,10 +1194,10 @@
         <v>13</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1211,10 +1211,10 @@
         <v>11</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1228,10 +1228,10 @@
         <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1245,10 +1245,10 @@
         <v>7</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1279,10 +1279,10 @@
         <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1296,10 +1296,10 @@
         <v>7</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1313,10 +1313,10 @@
         <v>13</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1330,10 +1330,10 @@
         <v>9</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1347,10 +1347,10 @@
         <v>7</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1364,10 +1364,10 @@
         <v>7</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1381,10 +1381,10 @@
         <v>7</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1398,10 +1398,10 @@
         <v>9</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1415,10 +1415,10 @@
         <v>7</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1432,10 +1432,10 @@
         <v>9</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1449,10 +1449,10 @@
         <v>11</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1466,10 +1466,10 @@
         <v>11</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1483,10 +1483,10 @@
         <v>7</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1517,10 +1517,10 @@
         <v>13</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1534,10 +1534,10 @@
         <v>11</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1551,10 +1551,10 @@
         <v>9</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1568,10 +1568,10 @@
         <v>13</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1585,10 +1585,10 @@
         <v>9</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1602,10 +1602,10 @@
         <v>9</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1619,10 +1619,10 @@
         <v>7</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1636,10 +1636,10 @@
         <v>9</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1653,10 +1653,10 @@
         <v>11</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1670,10 +1670,10 @@
         <v>13</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1687,10 +1687,10 @@
         <v>7</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1704,10 +1704,10 @@
         <v>13</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1721,10 +1721,10 @@
         <v>9</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1738,10 +1738,10 @@
         <v>29</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1755,10 +1755,10 @@
         <v>7</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1772,10 +1772,10 @@
         <v>5</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1789,10 +1789,10 @@
         <v>13</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1806,10 +1806,10 @@
         <v>13</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1823,10 +1823,10 @@
         <v>29</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1840,10 +1840,10 @@
         <v>9</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1857,10 +1857,10 @@
         <v>7</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1874,10 +1874,10 @@
         <v>9</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1891,10 +1891,10 @@
         <v>9</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1908,10 +1908,10 @@
         <v>29</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1925,10 +1925,10 @@
         <v>9</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1942,10 +1942,10 @@
         <v>7</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1959,10 +1959,10 @@
         <v>7</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1976,10 +1976,10 @@
         <v>9</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1993,10 +1993,10 @@
         <v>9</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2010,10 +2010,10 @@
         <v>7</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2027,10 +2027,10 @@
         <v>9</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2044,10 +2044,10 @@
         <v>11</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2061,10 +2061,10 @@
         <v>7</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2078,10 +2078,10 @@
         <v>9</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2095,10 +2095,10 @@
         <v>9</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2112,10 +2112,10 @@
         <v>9</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2129,10 +2129,10 @@
         <v>11</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2146,10 +2146,10 @@
         <v>29</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2163,10 +2163,10 @@
         <v>11</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2180,10 +2180,10 @@
         <v>29</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2197,10 +2197,10 @@
         <v>9</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2214,10 +2214,10 @@
         <v>9</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2231,10 +2231,10 @@
         <v>7</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2251,7 +2251,7 @@
         <v>157</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2282,10 +2282,10 @@
         <v>7</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2299,10 +2299,10 @@
         <v>5</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2316,10 +2316,10 @@
         <v>9</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2333,10 +2333,10 @@
         <v>9</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2350,10 +2350,10 @@
         <v>13</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2367,10 +2367,10 @@
         <v>7</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2384,10 +2384,10 @@
         <v>11</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2401,10 +2401,10 @@
         <v>7</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2418,10 +2418,10 @@
         <v>105</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2435,10 +2435,10 @@
         <v>13</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2452,10 +2452,10 @@
         <v>9</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2469,10 +2469,10 @@
         <v>7</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2486,10 +2486,10 @@
         <v>9</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2503,10 +2503,10 @@
         <v>7</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2520,10 +2520,10 @@
         <v>9</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2537,10 +2537,10 @@
         <v>9</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2554,10 +2554,10 @@
         <v>13</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2571,10 +2571,10 @@
         <v>13</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2588,10 +2588,10 @@
         <v>7</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2605,10 +2605,10 @@
         <v>7</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2622,10 +2622,10 @@
         <v>9</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2639,10 +2639,10 @@
         <v>7</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2656,10 +2656,10 @@
         <v>29</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2673,10 +2673,10 @@
         <v>9</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2690,10 +2690,10 @@
         <v>13</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2707,10 +2707,10 @@
         <v>13</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2724,10 +2724,10 @@
         <v>13</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2741,10 +2741,10 @@
         <v>13</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2758,10 +2758,10 @@
         <v>11</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2775,10 +2775,10 @@
         <v>9</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2792,10 +2792,10 @@
         <v>9</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2809,10 +2809,10 @@
         <v>11</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2829,7 +2829,7 @@
         <v>157</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2843,10 +2843,10 @@
         <v>7</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2860,10 +2860,10 @@
         <v>7</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -2877,10 +2877,10 @@
         <v>9</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2894,10 +2894,10 @@
         <v>7</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2914,7 +2914,7 @@
         <v>157</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2928,10 +2928,10 @@
         <v>7</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2945,10 +2945,10 @@
         <v>7</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2962,10 +2962,10 @@
         <v>9</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2979,10 +2979,10 @@
         <v>7</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2996,10 +2996,10 @@
         <v>11</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -3013,10 +3013,10 @@
         <v>11</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -3030,10 +3030,10 @@
         <v>9</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -3047,10 +3047,10 @@
         <v>9</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -3064,10 +3064,10 @@
         <v>7</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -3081,10 +3081,10 @@
         <v>7</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -3098,10 +3098,10 @@
         <v>7</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -3115,10 +3115,10 @@
         <v>13</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -3132,10 +3132,10 @@
         <v>13</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -3152,7 +3152,7 @@
         <v>157</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -3166,10 +3166,10 @@
         <v>7</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -3183,10 +3183,10 @@
         <v>7</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -3200,10 +3200,10 @@
         <v>13</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -3217,10 +3217,10 @@
         <v>7</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/upload/working_hour.xlsx
+++ b/upload/working_hour.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="159">
   <si>
     <t>Code</t>
   </si>
@@ -482,7 +482,10 @@
     <t>Upload Time</t>
   </si>
   <si>
-    <t>2024-02-24 18:36:29</t>
+    <t>2024-02-25 16:21:11</t>
+  </si>
+  <si>
+    <t>Success - No change</t>
   </si>
   <si>
     <t>Success</t>
@@ -1738,7 +1741,7 @@
         <v>29</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>155</v>
@@ -1925,7 +1928,7 @@
         <v>9</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>155</v>
@@ -1942,7 +1945,7 @@
         <v>7</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>155</v>
@@ -1976,7 +1979,7 @@
         <v>9</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>155</v>
@@ -2095,7 +2098,7 @@
         <v>9</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>155</v>
@@ -2248,7 +2251,7 @@
         <v>13</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>155</v>
@@ -2282,7 +2285,7 @@
         <v>7</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>155</v>
@@ -2452,7 +2455,7 @@
         <v>9</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>155</v>
@@ -2469,7 +2472,7 @@
         <v>7</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>155</v>
@@ -2503,7 +2506,7 @@
         <v>7</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>155</v>
@@ -2520,7 +2523,7 @@
         <v>9</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>155</v>
@@ -2554,7 +2557,7 @@
         <v>13</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>155</v>
@@ -2588,7 +2591,7 @@
         <v>7</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>155</v>
@@ -2605,7 +2608,7 @@
         <v>7</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>155</v>
@@ -2775,7 +2778,7 @@
         <v>9</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>155</v>
@@ -2826,7 +2829,7 @@
         <v>7</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>155</v>
@@ -2894,7 +2897,7 @@
         <v>7</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>155</v>
@@ -2911,7 +2914,7 @@
         <v>13</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>155</v>
@@ -2928,7 +2931,7 @@
         <v>7</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>155</v>
@@ -2979,7 +2982,7 @@
         <v>7</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>155</v>
@@ -3013,7 +3016,7 @@
         <v>11</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>155</v>
@@ -3115,7 +3118,7 @@
         <v>13</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>155</v>
@@ -3149,7 +3152,7 @@
         <v>7</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>155</v>
@@ -3166,7 +3169,7 @@
         <v>7</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>155</v>
@@ -3183,7 +3186,7 @@
         <v>7</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>155</v>
@@ -3200,7 +3203,7 @@
         <v>13</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>155</v>

--- a/upload/working_hour.xlsx
+++ b/upload/working_hour.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="158">
   <si>
     <t>Code</t>
   </si>
@@ -482,10 +482,7 @@
     <t>Upload Time</t>
   </si>
   <si>
-    <t>2024-02-25 16:21:11</t>
-  </si>
-  <si>
-    <t>Success - No change</t>
+    <t>2024-03-08 19:07:48</t>
   </si>
   <si>
     <t>Success</t>
@@ -1741,7 +1738,7 @@
         <v>29</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>155</v>
@@ -1928,7 +1925,7 @@
         <v>9</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>155</v>
@@ -1945,7 +1942,7 @@
         <v>7</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>155</v>
@@ -1979,7 +1976,7 @@
         <v>9</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>155</v>
@@ -2098,7 +2095,7 @@
         <v>9</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>155</v>
@@ -2251,7 +2248,7 @@
         <v>13</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>155</v>
@@ -2285,7 +2282,7 @@
         <v>7</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>155</v>
@@ -2455,7 +2452,7 @@
         <v>9</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>155</v>
@@ -2472,7 +2469,7 @@
         <v>7</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>155</v>
@@ -2506,7 +2503,7 @@
         <v>7</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>155</v>
@@ -2523,7 +2520,7 @@
         <v>9</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>155</v>
@@ -2557,7 +2554,7 @@
         <v>13</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>155</v>
@@ -2591,7 +2588,7 @@
         <v>7</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>155</v>
@@ -2608,7 +2605,7 @@
         <v>7</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>155</v>
@@ -2778,7 +2775,7 @@
         <v>9</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>155</v>
@@ -2829,7 +2826,7 @@
         <v>7</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>155</v>
@@ -2897,7 +2894,7 @@
         <v>7</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>155</v>
@@ -2914,7 +2911,7 @@
         <v>13</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>155</v>
@@ -2931,7 +2928,7 @@
         <v>7</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>155</v>
@@ -2982,7 +2979,7 @@
         <v>7</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>155</v>
@@ -3016,7 +3013,7 @@
         <v>11</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>155</v>
@@ -3118,7 +3115,7 @@
         <v>13</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>155</v>
@@ -3152,7 +3149,7 @@
         <v>7</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>155</v>
@@ -3169,7 +3166,7 @@
         <v>7</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>155</v>
@@ -3186,7 +3183,7 @@
         <v>7</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>155</v>
@@ -3203,7 +3200,7 @@
         <v>13</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>155</v>
